--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVIII/LTAIPT_A63F38B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVIII/LTAIPT_A63F38B.xlsx
@@ -1,28 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_9A306E32D6DFB0E19FC030DD919A5FA84821E2FB" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{74F0EB4C-30A6-4687-8402-990C36445A97}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_119">Hidden_1!$A$1:$A$26</definedName>
-    <definedName name="Hidden_223">Hidden_2!$A$1:$A$41</definedName>
-    <definedName name="Hidden_330">Hidden_3!$A$1:$A$32</definedName>
+    <definedName name="Hidden_117">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_220">Hidden_2!$A$1:$A$26</definedName>
+    <definedName name="Hidden_324">Hidden_3!$A$1:$A$41</definedName>
+    <definedName name="Hidden_431">Hidden_4!$A$1:$A$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="226">
   <si>
     <t>49003</t>
   </si>
@@ -114,6 +122,9 @@
     <t>436869</t>
   </si>
   <si>
+    <t>571943</t>
+  </si>
+  <si>
     <t>436870</t>
   </si>
   <si>
@@ -237,6 +248,9 @@
     <t xml:space="preserve">Segundo apellido del responsable de la gestión del trámite </t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Correo electrónico oficial</t>
   </si>
   <si>
@@ -309,15 +323,12 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Beca universal para estudiantes de educación media superior "Benito Juárez"</t>
   </si>
   <si>
-    <t>Becas</t>
-  </si>
-  <si>
     <t>No existe</t>
   </si>
   <si>
@@ -330,15 +341,15 @@
     <t>indefinido</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/Beca_Universal_para_Estudiantes_de_Educacion_Media_Superior.pdf</t>
+  </si>
+  <si>
     <t>Nombre, fecha de nacimiento, curp, matrícula, teléfono, correo electrónico y escolaridad</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20de%20Servicios%20Escolares/DOF%20-%20Diario%20Oficial%20de%20la%20Federaci%C3%B3n.pdf</t>
-  </si>
-  <si>
     <t>Griselda</t>
   </si>
   <si>
@@ -393,19 +404,31 @@
     <t>Subdirección de Servicios Educativos</t>
   </si>
   <si>
-    <t>Durante el periodo del 29 de agosto del  2022 al 27 de enero de 2023, el Colegio de Bachilleres del Estado de Tlaxcala, en el Programa de beca universal para estudiantes de educación media superior Benito Juárez, se encuentra de la siguiente manera: en la clave y denominación de partida presupuestal, los recursos son dispersados a los beneficiarios, directamente por la Coordinación Nacional de Becas para el Bienestar "Benito Juárez", por tanto no se tiene acceso a ello; los beneficiarios son ingresados por la dirección de cada plantel y aún se desconoce la manera en que haran llegar el recurso para  otorgarles su orden de pago y/o postulación y los jóvenes estudiantes acudan a realizar su cobro. Este proceso, depende del número de alumnos que se registren en la plataforma de becas, para después pasar a la validación que realiza la Coordinación Nacional de Becas para el Bienestar "Benito Juárez". No hay participación del Gobierno Estatal, sólo Federal. El monto es de $800.00 pesos mensuales no importando el género, el grado escolar ni el aprovechamiento académico. El presupuesto asignado al programa depende de la matrícula de alumnos vigente y puede variar cada semestre.</t>
-  </si>
-  <si>
-    <t>94B27B0FBEB255A070B7AC3B9C2512EE</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>13/01/2022</t>
+    <t>Becas Benito Juárez</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 28 de agosto de 2023 al 26 de enero de 2024, el Colegio de Bachilleres del Estado de Tlaxcala, en el Programa de beca universal para estudiantes de educación media superior Benito Juárez, se encuentra de la siguiente manera: en la clave y denominación de partida presupuestal, los recursos son dispersados a los beneficiarios, directamente por la Coordinación Nacional de Becas para el Bienestar "Benito Juárez", por tanto no se tiene acceso a ello; los beneficiarios son ingresados por la dirección de cada plantel y aún se desconoce la manera en que haran llegar el recurso para  otorgarles su orden de pago y/o postulación y los jóvenes estudiantes acudan a realizar su cobro. Este proceso, depende del número de alumnos que se registren en la plataforma de becas, para después pasar a la validación que realiza la Coordinación Nacional de Becas para el Bienestar "Benito Juárez". No hay participación del Gobierno Estatal, sólo Federal. El monto es de $875.00 pesos mensuales no importando el género, el grado escolar ni el aprovechamiento académico. El presupuesto asignado al programa depende de la matrícula de alumnos vigente y puede variar cada semestre.</t>
+  </si>
+  <si>
+    <t>CA106145E1CED0C9BB614817A4F8D2A2</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>11/01/2024</t>
+  </si>
+  <si>
+    <t>Hombre</t>
   </si>
   <si>
     <t>Carretera</t>
@@ -690,7 +713,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -786,6 +809,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -801,44 +827,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -866,14 +892,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -901,6 +944,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -912,175 +972,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AP8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1090,45 +1126,46 @@
     <col min="8" max="8" width="70.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="158" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="153.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="75.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="158" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="153.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="69.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="61.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="20" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="255" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="69.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1145,7 +1182,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1160,7 +1197,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1210,49 +1247,49 @@
         <v>6</v>
       </c>
       <c r="R4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S4" t="s">
         <v>6</v>
       </c>
       <c r="T4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U4" t="s">
         <v>11</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>8</v>
-      </c>
-      <c r="V4" t="s">
-        <v>6</v>
       </c>
       <c r="W4" t="s">
         <v>6</v>
       </c>
       <c r="X4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>8</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>8</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>6</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>8</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>6</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>11</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>6</v>
       </c>
       <c r="AG4" t="s">
         <v>6</v>
@@ -1270,19 +1307,22 @@
         <v>6</v>
       </c>
       <c r="AL4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM4" t="s">
         <v>8</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>7</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>12</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1403,10 +1443,13 @@
       <c r="AO5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1448,183 +1491,187 @@
       <c r="AM6" s="4"/>
       <c r="AN6" s="4"/>
       <c r="AO6" s="4"/>
-    </row>
-    <row r="7" spans="1:41" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AP6" s="4"/>
+    </row>
+    <row r="7" spans="1:42" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="N8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>109</v>
@@ -1639,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>114</v>
@@ -1651,22 +1698,22 @@
         <v>115</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>118</v>
@@ -1684,21 +1731,24 @@
         <v>122</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP8" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="AN8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AO6"/>
+    <mergeCell ref="A6:AP6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1706,15 +1756,18 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T8:T198">
-      <formula1>Hidden_119</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R8:R198" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>Hidden_117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X198">
-      <formula1>Hidden_223</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U8:U198" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>Hidden_220</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE8:AE198">
-      <formula1>Hidden_330</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y198" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>Hidden_324</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF198" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>Hidden_431</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1722,138 +1775,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1862,213 +1795,138 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2077,168 +1935,383 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
